--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/overall_importance.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/overall_importance.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1553119149763115</v>
+        <v>0.1555220890712872</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1405418980007257</v>
+        <v>0.1404667031911174</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1368584099833477</v>
+        <v>0.1370318434941518</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1347412907074057</v>
+        <v>0.1366752411923378</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1345016126063231</v>
+        <v>0.1333377488489045</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.132684382319427</v>
+        <v>0.131606685423989</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1298060888817821</v>
+        <v>0.1302285678437683</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03555440252467725</v>
+        <v>0.03513112093444412</v>
       </c>
     </row>
   </sheetData>
